--- a/Отчёт.xlsx
+++ b/Отчёт.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Projects\СОЭЗ\Telegram\form_kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D4F14C-2980-4E33-A0A3-AF64BD0EDD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92209CAB-16A1-4F8E-AA1A-3E76B8C45792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{896FA051-009E-4318-B742-8FCF3A1B02A5}"/>
   </bookViews>
@@ -22,6 +22,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1223,12 +1234,192 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1239,186 +1430,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1770,282 +1781,282 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
-      <c r="AH1" s="103"/>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="103"/>
-      <c r="AK1" s="103"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
+      <c r="AC1" s="85"/>
+      <c r="AD1" s="85"/>
+      <c r="AE1" s="85"/>
+      <c r="AF1" s="85"/>
+      <c r="AG1" s="85"/>
+      <c r="AH1" s="85"/>
+      <c r="AI1" s="85"/>
+      <c r="AJ1" s="85"/>
+      <c r="AK1" s="85"/>
       <c r="AL1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="L2" s="96" t="s">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="L2" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
       <c r="Q2" s="5"/>
-      <c r="R2" s="126" t="s">
+      <c r="R2" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
-      <c r="U2" s="126"/>
-      <c r="V2" s="126"/>
-      <c r="W2" s="126"/>
-      <c r="X2" s="126"/>
-      <c r="Y2" s="126"/>
-      <c r="Z2" s="126"/>
-      <c r="AA2" s="126"/>
-      <c r="AB2" s="126"/>
-      <c r="AC2" s="126"/>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="126"/>
-      <c r="AG2" s="126"/>
-      <c r="AH2" s="126"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="62"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:38" s="7" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="105" t="s">
+      <c r="A4" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="113" t="s">
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="114"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="97" t="s">
+      <c r="R4" s="72"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="98"/>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="99"/>
+      <c r="U4" s="87"/>
+      <c r="V4" s="87"/>
+      <c r="W4" s="87"/>
+      <c r="X4" s="87"/>
+      <c r="Y4" s="87"/>
+      <c r="Z4" s="87"/>
+      <c r="AA4" s="87"/>
+      <c r="AB4" s="87"/>
+      <c r="AC4" s="87"/>
+      <c r="AD4" s="87"/>
+      <c r="AE4" s="87"/>
+      <c r="AF4" s="87"/>
+      <c r="AG4" s="87"/>
+      <c r="AH4" s="87"/>
+      <c r="AI4" s="87"/>
+      <c r="AJ4" s="87"/>
+      <c r="AK4" s="88"/>
       <c r="AL4" s="6"/>
     </row>
     <row r="5" spans="1:38" s="9" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="106"/>
-      <c r="B5" s="106"/>
-      <c r="C5" s="100" t="s">
+      <c r="A5" s="92"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="102" t="s">
+      <c r="F5" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="102" t="s">
+      <c r="G5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="102" t="s">
+      <c r="H5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="102" t="s">
+      <c r="I5" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="102" t="s">
+      <c r="K5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="102" t="s">
+      <c r="L5" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="102" t="s">
+      <c r="M5" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="102" t="s">
+      <c r="N5" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="102" t="s">
+      <c r="O5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="112" t="s">
+      <c r="P5" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="104" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="68" t="s">
+      <c r="U5" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="68" t="s">
+      <c r="V5" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="68" t="s">
+      <c r="W5" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="X5" s="68" t="s">
+      <c r="X5" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="110" t="s">
+      <c r="Y5" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="110" t="s">
+      <c r="Z5" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AA5" s="68" t="s">
+      <c r="AA5" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="68" t="s">
+      <c r="AB5" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="122" t="s">
+      <c r="AC5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="110" t="s">
+      <c r="AD5" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="110"/>
-      <c r="AF5" s="124" t="s">
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" s="68" t="s">
+      <c r="AG5" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="AH5" s="68" t="s">
+      <c r="AH5" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="AI5" s="68" t="s">
+      <c r="AI5" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AJ5" s="68" t="s">
+      <c r="AJ5" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="AK5" s="108" t="s">
+      <c r="AK5" s="94" t="s">
         <v>30</v>
       </c>
       <c r="AL5" s="8"/>
     </row>
     <row r="6" spans="1:38" s="9" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="107"/>
-      <c r="B6" s="107"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="121"/>
-      <c r="T6" s="101"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="111"/>
-      <c r="AA6" s="69"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="123"/>
+      <c r="A6" s="93"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="96"/>
+      <c r="Z6" s="96"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="82"/>
       <c r="AD6" s="54" t="s">
         <v>42</v>
       </c>
       <c r="AE6" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="AF6" s="125"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="109"/>
+      <c r="AF6" s="84"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="70"/>
       <c r="AL6" s="8"/>
     </row>
-    <row r="7" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53" t="s">
         <v>112</v>
       </c>
@@ -2066,11 +2077,11 @@
       <c r="N7" s="50"/>
       <c r="O7" s="50"/>
       <c r="P7" s="52"/>
-      <c r="Q7" s="86" t="s">
+      <c r="Q7" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="R7" s="87"/>
-      <c r="S7" s="88"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="104"/>
       <c r="T7" s="55" t="s">
         <v>73</v>
       </c>
@@ -2144,9 +2155,9 @@
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="13"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="91"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="106"/>
+      <c r="S8" s="107"/>
       <c r="T8" s="30"/>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
@@ -2184,9 +2195,9 @@
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="89"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="91"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="106"/>
+      <c r="S9" s="107"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
@@ -2224,9 +2235,9 @@
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="90"/>
-      <c r="S10" s="91"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="107"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
@@ -2264,9 +2275,9 @@
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
       <c r="P11" s="13"/>
-      <c r="Q11" s="92"/>
-      <c r="R11" s="93"/>
-      <c r="S11" s="94"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="110"/>
       <c r="T11" s="19"/>
       <c r="U11" s="19"/>
       <c r="V11" s="19"/>
@@ -2304,9 +2315,9 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="13"/>
-      <c r="Q12" s="95"/>
-      <c r="R12" s="95"/>
-      <c r="S12" s="95"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
@@ -2344,9 +2355,9 @@
       <c r="N13" s="19"/>
       <c r="O13" s="19"/>
       <c r="P13" s="13"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="94"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="110"/>
       <c r="T13" s="19"/>
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
@@ -2384,9 +2395,9 @@
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="13"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
@@ -2409,11 +2420,11 @@
     </row>
     <row r="15" spans="1:38" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95"/>
+      <c r="P15" s="95"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="21"/>
@@ -2436,59 +2447,59 @@
       <c r="AJ15" s="5"/>
     </row>
     <row r="16" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="71"/>
-      <c r="W16" s="71"/>
-      <c r="X16" s="72"/>
-      <c r="Y16" s="73" t="s">
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="113"/>
+      <c r="T16" s="113"/>
+      <c r="U16" s="113"/>
+      <c r="V16" s="113"/>
+      <c r="W16" s="113"/>
+      <c r="X16" s="114"/>
+      <c r="Y16" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="74"/>
-      <c r="AB16" s="75"/>
-      <c r="AC16" s="76" t="s">
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="116"/>
+      <c r="AB16" s="117"/>
+      <c r="AC16" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="AD16" s="77"/>
-      <c r="AE16" s="76" t="s">
+      <c r="AD16" s="119"/>
+      <c r="AE16" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="80"/>
-      <c r="AG16" s="80"/>
-      <c r="AH16" s="80"/>
-      <c r="AI16" s="80"/>
-      <c r="AJ16" s="80"/>
-      <c r="AK16" s="77"/>
+      <c r="AF16" s="122"/>
+      <c r="AG16" s="122"/>
+      <c r="AH16" s="122"/>
+      <c r="AI16" s="122"/>
+      <c r="AJ16" s="122"/>
+      <c r="AK16" s="119"/>
     </row>
     <row r="17" spans="1:63" ht="135.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
-      <c r="B17" s="85"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="40" t="s">
         <v>46</v>
       </c>
@@ -2567,21 +2578,21 @@
       <c r="AB17" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="AC17" s="78"/>
-      <c r="AD17" s="79"/>
-      <c r="AE17" s="78"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="79"/>
+      <c r="AC17" s="120"/>
+      <c r="AD17" s="121"/>
+      <c r="AE17" s="120"/>
+      <c r="AF17" s="123"/>
+      <c r="AG17" s="123"/>
+      <c r="AH17" s="123"/>
+      <c r="AI17" s="123"/>
+      <c r="AJ17" s="123"/>
+      <c r="AK17" s="121"/>
       <c r="AL17" s="22"/>
       <c r="AM17" s="23"/>
       <c r="AN17" s="5"/>
       <c r="BK17" s="2"/>
     </row>
-    <row r="18" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:63" ht="99" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>112</v>
       </c>
@@ -2664,17 +2675,17 @@
         <v>68</v>
       </c>
       <c r="AB18" s="39"/>
-      <c r="AC18" s="65"/>
-      <c r="AD18" s="66"/>
-      <c r="AE18" s="64" t="s">
+      <c r="AC18" s="125"/>
+      <c r="AD18" s="126"/>
+      <c r="AE18" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="AF18" s="65"/>
-      <c r="AG18" s="65"/>
-      <c r="AH18" s="65"/>
-      <c r="AI18" s="65"/>
-      <c r="AJ18" s="65"/>
-      <c r="AK18" s="66"/>
+      <c r="AF18" s="125"/>
+      <c r="AG18" s="125"/>
+      <c r="AH18" s="125"/>
+      <c r="AI18" s="125"/>
+      <c r="AJ18" s="125"/>
+      <c r="AK18" s="126"/>
       <c r="AL18" s="27"/>
       <c r="AM18" s="28"/>
       <c r="AN18" s="5"/>
@@ -2709,15 +2720,15 @@
       <c r="Z19" s="26"/>
       <c r="AA19" s="32"/>
       <c r="AB19" s="34"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="63"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="63"/>
+      <c r="AC19" s="64"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="127"/>
+      <c r="AF19" s="64"/>
+      <c r="AG19" s="64"/>
+      <c r="AH19" s="64"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="64"/>
+      <c r="AK19" s="65"/>
       <c r="AL19" s="27"/>
       <c r="AM19" s="28"/>
       <c r="AN19" s="5"/>
@@ -2752,15 +2763,15 @@
       <c r="Z20" s="26"/>
       <c r="AA20" s="32"/>
       <c r="AB20" s="34"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="63"/>
-      <c r="AE20" s="67"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="63"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="65"/>
+      <c r="AE20" s="127"/>
+      <c r="AF20" s="64"/>
+      <c r="AG20" s="64"/>
+      <c r="AH20" s="64"/>
+      <c r="AI20" s="64"/>
+      <c r="AJ20" s="64"/>
+      <c r="AK20" s="65"/>
       <c r="AL20" s="27"/>
       <c r="AM20" s="28"/>
       <c r="AN20" s="5"/>
@@ -2795,15 +2806,15 @@
       <c r="Z21" s="26"/>
       <c r="AA21" s="32"/>
       <c r="AB21" s="34"/>
-      <c r="AC21" s="62"/>
-      <c r="AD21" s="63"/>
-      <c r="AE21" s="67"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="63"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="65"/>
+      <c r="AE21" s="127"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="64"/>
+      <c r="AJ21" s="64"/>
+      <c r="AK21" s="65"/>
       <c r="AL21" s="27"/>
       <c r="AM21" s="28"/>
       <c r="AN21" s="5"/>
@@ -2838,15 +2849,15 @@
       <c r="Z22" s="26"/>
       <c r="AA22" s="32"/>
       <c r="AB22" s="34"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="63"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="63"/>
+      <c r="AC22" s="64"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="127"/>
+      <c r="AF22" s="64"/>
+      <c r="AG22" s="64"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="65"/>
       <c r="AL22" s="27"/>
       <c r="AM22" s="28"/>
       <c r="AN22" s="5"/>
@@ -2881,15 +2892,15 @@
       <c r="Z23" s="26"/>
       <c r="AA23" s="32"/>
       <c r="AB23" s="34"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="63"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="127"/>
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="65"/>
       <c r="AL23" s="27"/>
       <c r="AM23" s="28"/>
       <c r="AN23" s="5"/>
@@ -2924,15 +2935,15 @@
       <c r="Z24" s="26"/>
       <c r="AA24" s="32"/>
       <c r="AB24" s="34"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="63"/>
-      <c r="AE24" s="67"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="63"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="127"/>
+      <c r="AF24" s="64"/>
+      <c r="AG24" s="64"/>
+      <c r="AH24" s="64"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="64"/>
+      <c r="AK24" s="65"/>
       <c r="AL24" s="27"/>
       <c r="AM24" s="28"/>
       <c r="AN24" s="5"/>
@@ -2967,15 +2978,15 @@
       <c r="Z25" s="26"/>
       <c r="AA25" s="32"/>
       <c r="AB25" s="34"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="63"/>
-      <c r="AE25" s="67"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="63"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="65"/>
+      <c r="AE25" s="127"/>
+      <c r="AF25" s="64"/>
+      <c r="AG25" s="64"/>
+      <c r="AH25" s="64"/>
+      <c r="AI25" s="64"/>
+      <c r="AJ25" s="64"/>
+      <c r="AK25" s="65"/>
       <c r="AL25" s="27"/>
       <c r="AM25" s="28"/>
       <c r="AN25" s="5"/>
@@ -3010,15 +3021,15 @@
       <c r="Z26" s="36"/>
       <c r="AA26" s="37"/>
       <c r="AB26" s="38"/>
-      <c r="AC26" s="62"/>
-      <c r="AD26" s="63"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="62"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="62"/>
-      <c r="AJ26" s="62"/>
-      <c r="AK26" s="63"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="65"/>
+      <c r="AE26" s="127"/>
+      <c r="AF26" s="64"/>
+      <c r="AG26" s="64"/>
+      <c r="AH26" s="64"/>
+      <c r="AI26" s="64"/>
+      <c r="AJ26" s="64"/>
+      <c r="AK26" s="65"/>
       <c r="AL26" s="27"/>
       <c r="AM26" s="28"/>
       <c r="AN26" s="5"/>
@@ -3029,6 +3040,63 @@
     <row r="29" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="AE18:AK18"/>
+    <mergeCell ref="AE19:AK19"/>
+    <mergeCell ref="AE20:AK20"/>
+    <mergeCell ref="AE21:AK21"/>
+    <mergeCell ref="AE22:AK22"/>
+    <mergeCell ref="AE23:AK23"/>
+    <mergeCell ref="AE24:AK24"/>
+    <mergeCell ref="AE25:AK25"/>
+    <mergeCell ref="AE26:AK26"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="C16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="AC16:AD17"/>
+    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="C4:P4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="T4:AK4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="L2:P2"/>
     <mergeCell ref="R2:AH2"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="AC24:AD24"/>
@@ -3045,63 +3113,6 @@
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q4:S6"/>
     <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="C4:P4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="C16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="AC16:AD17"/>
-    <mergeCell ref="AE16:AK17"/>
-    <mergeCell ref="AC26:AD26"/>
-    <mergeCell ref="AE18:AK18"/>
-    <mergeCell ref="AE19:AK19"/>
-    <mergeCell ref="AE20:AK20"/>
-    <mergeCell ref="AE21:AK21"/>
-    <mergeCell ref="AE22:AK22"/>
-    <mergeCell ref="AE23:AK23"/>
-    <mergeCell ref="AE24:AK24"/>
-    <mergeCell ref="AE25:AK25"/>
-    <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="AC23:AD23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Отчёт.xlsx
+++ b/Отчёт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Projects\СОЭЗ\Telegram\form_kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92209CAB-16A1-4F8E-AA1A-3E76B8C45792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672218A0-6752-45B3-905F-4D43A81A1D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{896FA051-009E-4318-B742-8FCF3A1B02A5}"/>
   </bookViews>
@@ -392,7 +392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +478,29 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1133,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1160,15 +1183,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1177,22 +1194,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1203,13 +1208,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1228,39 +1226,150 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1288,149 +1397,119 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1781,139 +1860,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="85"/>
-      <c r="AF1" s="85"/>
-      <c r="AG1" s="85"/>
-      <c r="AH1" s="85"/>
-      <c r="AI1" s="85"/>
-      <c r="AJ1" s="85"/>
-      <c r="AK1" s="85"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
+      <c r="AH1" s="73"/>
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="73"/>
       <c r="AL1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="L2" s="95" t="s">
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="L2" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
       <c r="Q2" s="5"/>
-      <c r="R2" s="62" t="s">
+      <c r="R2" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="62"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="62"/>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="62"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="62"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:38" s="7" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="71" t="s">
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="72"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="86" t="s">
+      <c r="R4" s="84"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="87"/>
-      <c r="AC4" s="87"/>
-      <c r="AD4" s="87"/>
-      <c r="AE4" s="87"/>
-      <c r="AF4" s="87"/>
-      <c r="AG4" s="87"/>
-      <c r="AH4" s="87"/>
-      <c r="AI4" s="87"/>
-      <c r="AJ4" s="87"/>
-      <c r="AK4" s="88"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="64"/>
+      <c r="AE4" s="64"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="64"/>
+      <c r="AK4" s="65"/>
       <c r="AL4" s="6"/>
     </row>
     <row r="5" spans="1:38" s="9" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="97" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="66" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="68" t="s">
@@ -1952,191 +2031,191 @@
       <c r="O5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="89" t="s">
+      <c r="Q5" s="86"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="88"/>
+      <c r="T5" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="66" t="s">
+      <c r="U5" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="66" t="s">
+      <c r="V5" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="66" t="s">
+      <c r="W5" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="X5" s="66" t="s">
+      <c r="X5" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="80" t="s">
+      <c r="Y5" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="80" t="s">
+      <c r="Z5" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="AA5" s="66" t="s">
+      <c r="AA5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="66" t="s">
+      <c r="AB5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="81" t="s">
+      <c r="AC5" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="80"/>
-      <c r="AF5" s="83" t="s">
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" s="66" t="s">
+      <c r="AG5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="AH5" s="66" t="s">
+      <c r="AH5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="AI5" s="66" t="s">
+      <c r="AI5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="AJ5" s="66" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="AK5" s="94" t="s">
+      <c r="AK5" s="78" t="s">
         <v>30</v>
       </c>
       <c r="AL5" s="8"/>
     </row>
     <row r="6" spans="1:38" s="9" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="96"/>
-      <c r="Z6" s="96"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="82"/>
-      <c r="AD6" s="54" t="s">
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="89"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
+      <c r="AC6" s="70"/>
+      <c r="AD6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="AE6" s="54" t="s">
+      <c r="AE6" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="AF6" s="84"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="70"/>
+      <c r="AF6" s="72"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="79"/>
       <c r="AL6" s="8"/>
     </row>
     <row r="7" spans="1:38" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="102" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="R7" s="103"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="55" t="s">
+      <c r="R7" s="58"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="U7" s="55" t="s">
+      <c r="U7" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="V7" s="55" t="s">
+      <c r="V7" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="W7" s="55" t="s">
+      <c r="W7" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="X7" s="55" t="s">
+      <c r="X7" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="Y7" s="55" t="s">
+      <c r="Y7" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="Z7" s="55" t="s">
+      <c r="Z7" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="AA7" s="55" t="s">
+      <c r="AA7" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="AB7" s="55" t="s">
+      <c r="AB7" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="AC7" s="55" t="s">
+      <c r="AC7" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="AD7" s="55" t="s">
+      <c r="AD7" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="AE7" s="55" t="s">
+      <c r="AE7" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="AF7" s="55" t="s">
+      <c r="AF7" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="AG7" s="55" t="s">
+      <c r="AG7" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="AH7" s="55" t="s">
+      <c r="AH7" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="AI7" s="55" t="s">
+      <c r="AI7" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="AJ7" s="55" t="s">
+      <c r="AJ7" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="AK7" s="55" t="s">
+      <c r="AK7" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="AL7" s="17"/>
+      <c r="AL7" s="14"/>
     </row>
     <row r="8" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
@@ -2155,28 +2234,28 @@
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="13"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="106"/>
-      <c r="S8" s="107"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="30"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="17"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="93"/>
+      <c r="U8" s="93"/>
+      <c r="V8" s="93"/>
+      <c r="W8" s="93"/>
+      <c r="X8" s="93"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="93"/>
+      <c r="AA8" s="93"/>
+      <c r="AB8" s="93"/>
+      <c r="AC8" s="93"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="93"/>
+      <c r="AF8" s="93"/>
+      <c r="AG8" s="93"/>
+      <c r="AH8" s="93"/>
+      <c r="AI8" s="93"/>
+      <c r="AJ8" s="93"/>
+      <c r="AK8" s="94"/>
+      <c r="AL8" s="14"/>
     </row>
     <row r="9" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
@@ -2195,28 +2274,28 @@
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="106"/>
-      <c r="S9" s="107"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="14"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="15"/>
-      <c r="AK9" s="16"/>
-      <c r="AL9" s="17"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="94"/>
+      <c r="AC9" s="94"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="94"/>
+      <c r="AG9" s="95"/>
+      <c r="AH9" s="94"/>
+      <c r="AI9" s="94"/>
+      <c r="AJ9" s="92"/>
+      <c r="AK9" s="94"/>
+      <c r="AL9" s="14"/>
     </row>
     <row r="10" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
@@ -2235,68 +2314,68 @@
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="107"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="11"/>
-      <c r="AG10" s="14"/>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="16"/>
-      <c r="AJ10" s="15"/>
-      <c r="AK10" s="16"/>
-      <c r="AL10" s="17"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="100"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="94"/>
+      <c r="X10" s="94"/>
+      <c r="Y10" s="94"/>
+      <c r="Z10" s="94"/>
+      <c r="AA10" s="94"/>
+      <c r="AB10" s="94"/>
+      <c r="AC10" s="94"/>
+      <c r="AD10" s="94"/>
+      <c r="AE10" s="94"/>
+      <c r="AF10" s="94"/>
+      <c r="AG10" s="95"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="94"/>
+      <c r="AJ10" s="92"/>
+      <c r="AK10" s="94"/>
+      <c r="AL10" s="14"/>
     </row>
     <row r="11" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="12"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
       <c r="P11" s="13"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="20"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="15"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="17"/>
+      <c r="Q11" s="101"/>
+      <c r="R11" s="102"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="96"/>
+      <c r="U11" s="96"/>
+      <c r="V11" s="96"/>
+      <c r="W11" s="96"/>
+      <c r="X11" s="96"/>
+      <c r="Y11" s="94"/>
+      <c r="Z11" s="94"/>
+      <c r="AA11" s="96"/>
+      <c r="AB11" s="96"/>
+      <c r="AC11" s="96"/>
+      <c r="AD11" s="96"/>
+      <c r="AE11" s="96"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="97"/>
+      <c r="AH11" s="94"/>
+      <c r="AI11" s="94"/>
+      <c r="AJ11" s="92"/>
+      <c r="AK11" s="94"/>
+      <c r="AL11" s="14"/>
     </row>
     <row r="12" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
@@ -2315,68 +2394,68 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="13"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="11"/>
-      <c r="AG12" s="14"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="16"/>
-      <c r="AL12" s="17"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="94"/>
+      <c r="X12" s="94"/>
+      <c r="Y12" s="94"/>
+      <c r="Z12" s="94"/>
+      <c r="AA12" s="94"/>
+      <c r="AB12" s="94"/>
+      <c r="AC12" s="94"/>
+      <c r="AD12" s="94"/>
+      <c r="AE12" s="94"/>
+      <c r="AF12" s="94"/>
+      <c r="AG12" s="95"/>
+      <c r="AH12" s="94"/>
+      <c r="AI12" s="94"/>
+      <c r="AJ12" s="92"/>
+      <c r="AK12" s="94"/>
+      <c r="AL12" s="14"/>
     </row>
     <row r="13" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="12"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
       <c r="P13" s="13"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="109"/>
-      <c r="S13" s="110"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="20"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="15"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="17"/>
+      <c r="Q13" s="101"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="96"/>
+      <c r="U13" s="96"/>
+      <c r="V13" s="96"/>
+      <c r="W13" s="96"/>
+      <c r="X13" s="96"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="96"/>
+      <c r="AB13" s="96"/>
+      <c r="AC13" s="96"/>
+      <c r="AD13" s="96"/>
+      <c r="AE13" s="96"/>
+      <c r="AF13" s="96"/>
+      <c r="AG13" s="97"/>
+      <c r="AH13" s="94"/>
+      <c r="AI13" s="94"/>
+      <c r="AJ13" s="92"/>
+      <c r="AK13" s="94"/>
+      <c r="AL13" s="14"/>
     </row>
     <row r="14" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
@@ -2395,39 +2474,39 @@
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="13"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="11"/>
-      <c r="AG14" s="14"/>
-      <c r="AH14" s="16"/>
-      <c r="AI14" s="16"/>
-      <c r="AJ14" s="15"/>
-      <c r="AK14" s="16"/>
-      <c r="AL14" s="17"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="104"/>
+      <c r="S14" s="104"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="94"/>
+      <c r="Z14" s="94"/>
+      <c r="AA14" s="94"/>
+      <c r="AB14" s="94"/>
+      <c r="AC14" s="94"/>
+      <c r="AD14" s="94"/>
+      <c r="AE14" s="94"/>
+      <c r="AF14" s="94"/>
+      <c r="AG14" s="95"/>
+      <c r="AH14" s="94"/>
+      <c r="AI14" s="94"/>
+      <c r="AJ14" s="92"/>
+      <c r="AK14" s="94"/>
+      <c r="AL14" s="14"/>
     </row>
     <row r="15" spans="1:38" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="95"/>
-      <c r="P15" s="95"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="60"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="21"/>
+      <c r="S15" s="17"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -2447,591 +2526,591 @@
       <c r="AJ15" s="5"/>
     </row>
     <row r="16" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="112" t="s">
+      <c r="C16" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="113"/>
-      <c r="U16" s="113"/>
-      <c r="V16" s="113"/>
-      <c r="W16" s="113"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="115" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="42"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="Z16" s="116"/>
-      <c r="AA16" s="116"/>
-      <c r="AB16" s="117"/>
-      <c r="AC16" s="118" t="s">
+      <c r="Z16" s="45"/>
+      <c r="AA16" s="45"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="AD16" s="119"/>
-      <c r="AE16" s="118" t="s">
+      <c r="AD16" s="48"/>
+      <c r="AE16" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="122"/>
-      <c r="AG16" s="122"/>
-      <c r="AH16" s="122"/>
-      <c r="AI16" s="122"/>
-      <c r="AJ16" s="122"/>
-      <c r="AK16" s="119"/>
+      <c r="AF16" s="51"/>
+      <c r="AG16" s="51"/>
+      <c r="AH16" s="51"/>
+      <c r="AI16" s="51"/>
+      <c r="AJ16" s="51"/>
+      <c r="AK16" s="48"/>
     </row>
     <row r="17" spans="1:63" ht="135.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="99"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="40" t="s">
+      <c r="A17" s="54"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="41" t="s">
+      <c r="I17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="41" t="s">
+      <c r="K17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="L17" s="41" t="s">
+      <c r="L17" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="41" t="s">
+      <c r="N17" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="O17" s="41" t="s">
+      <c r="O17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="P17" s="41" t="s">
+      <c r="P17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="Q17" s="41" t="s">
+      <c r="Q17" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="41" t="s">
+      <c r="R17" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="S17" s="41" t="s">
+      <c r="S17" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="T17" s="41" t="s">
+      <c r="T17" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="U17" s="41" t="s">
+      <c r="U17" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="V17" s="41" t="s">
+      <c r="V17" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="W17" s="41" t="s">
+      <c r="W17" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="X17" s="56" t="s">
+      <c r="X17" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="Y17" s="40" t="s">
+      <c r="Y17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="Z17" s="41" t="s">
+      <c r="Z17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="AA17" s="41" t="s">
+      <c r="AA17" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="AB17" s="42" t="s">
+      <c r="AB17" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="121"/>
-      <c r="AE17" s="120"/>
-      <c r="AF17" s="123"/>
-      <c r="AG17" s="123"/>
-      <c r="AH17" s="123"/>
-      <c r="AI17" s="123"/>
-      <c r="AJ17" s="123"/>
-      <c r="AK17" s="121"/>
-      <c r="AL17" s="22"/>
-      <c r="AM17" s="23"/>
+      <c r="AC17" s="49"/>
+      <c r="AD17" s="50"/>
+      <c r="AE17" s="49"/>
+      <c r="AF17" s="52"/>
+      <c r="AG17" s="52"/>
+      <c r="AH17" s="52"/>
+      <c r="AI17" s="52"/>
+      <c r="AJ17" s="52"/>
+      <c r="AK17" s="50"/>
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="19"/>
       <c r="AN17" s="5"/>
       <c r="BK17" s="2"/>
     </row>
     <row r="18" spans="1:63" ht="99" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="F18" s="55" t="s">
+      <c r="F18" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="55" t="s">
+      <c r="I18" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="55" t="s">
+      <c r="J18" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="K18" s="55" t="s">
+      <c r="K18" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="55" t="s">
+      <c r="L18" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="M18" s="55" t="s">
+      <c r="M18" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="N18" s="55" t="s">
+      <c r="N18" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="O18" s="55" t="s">
+      <c r="O18" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="55" t="s">
+      <c r="P18" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="Q18" s="55" t="s">
+      <c r="Q18" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="R18" s="55" t="s">
+      <c r="R18" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="S18" s="55" t="s">
+      <c r="S18" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="T18" s="55" t="s">
+      <c r="T18" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="U18" s="55" t="s">
+      <c r="U18" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="V18" s="55" t="s">
+      <c r="V18" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="W18" s="55" t="s">
+      <c r="W18" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="X18" s="57" t="s">
+      <c r="X18" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="Y18" s="61" t="s">
+      <c r="Y18" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="Z18" s="55" t="s">
+      <c r="Z18" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="AA18" s="55" t="s">
+      <c r="AA18" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="AB18" s="39"/>
-      <c r="AC18" s="125"/>
-      <c r="AD18" s="126"/>
-      <c r="AE18" s="124" t="s">
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="37"/>
+      <c r="AD18" s="38"/>
+      <c r="AE18" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="AF18" s="125"/>
-      <c r="AG18" s="125"/>
-      <c r="AH18" s="125"/>
-      <c r="AI18" s="125"/>
-      <c r="AJ18" s="125"/>
-      <c r="AK18" s="126"/>
-      <c r="AL18" s="27"/>
-      <c r="AM18" s="28"/>
+      <c r="AF18" s="37"/>
+      <c r="AG18" s="37"/>
+      <c r="AH18" s="37"/>
+      <c r="AI18" s="37"/>
+      <c r="AJ18" s="37"/>
+      <c r="AK18" s="38"/>
+      <c r="AL18" s="21"/>
+      <c r="AM18" s="22"/>
       <c r="AN18" s="5"/>
       <c r="BK18" s="2"/>
     </row>
     <row r="19" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="58"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="64"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="127"/>
-      <c r="AF19" s="64"/>
-      <c r="AG19" s="64"/>
-      <c r="AH19" s="64"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="64"/>
-      <c r="AK19" s="65"/>
-      <c r="AL19" s="27"/>
-      <c r="AM19" s="28"/>
+      <c r="A19" s="108"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="109"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="109"/>
+      <c r="U19" s="109"/>
+      <c r="V19" s="109"/>
+      <c r="W19" s="109"/>
+      <c r="X19" s="110"/>
+      <c r="Y19" s="111"/>
+      <c r="Z19" s="112"/>
+      <c r="AA19" s="108"/>
+      <c r="AB19" s="113"/>
+      <c r="AC19" s="105"/>
+      <c r="AD19" s="106"/>
+      <c r="AE19" s="107"/>
+      <c r="AF19" s="105"/>
+      <c r="AG19" s="105"/>
+      <c r="AH19" s="105"/>
+      <c r="AI19" s="105"/>
+      <c r="AJ19" s="105"/>
+      <c r="AK19" s="106"/>
+      <c r="AL19" s="21"/>
+      <c r="AM19" s="22"/>
       <c r="AN19" s="5"/>
       <c r="BK19" s="2"/>
     </row>
     <row r="20" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="59"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="64"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="127"/>
-      <c r="AF20" s="64"/>
-      <c r="AG20" s="64"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="64"/>
-      <c r="AJ20" s="64"/>
-      <c r="AK20" s="65"/>
-      <c r="AL20" s="27"/>
-      <c r="AM20" s="28"/>
+      <c r="A20" s="108"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="109"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="109"/>
+      <c r="V20" s="109"/>
+      <c r="W20" s="116"/>
+      <c r="X20" s="117"/>
+      <c r="Y20" s="111"/>
+      <c r="Z20" s="112"/>
+      <c r="AA20" s="108"/>
+      <c r="AB20" s="113"/>
+      <c r="AC20" s="105"/>
+      <c r="AD20" s="106"/>
+      <c r="AE20" s="107"/>
+      <c r="AF20" s="105"/>
+      <c r="AG20" s="105"/>
+      <c r="AH20" s="105"/>
+      <c r="AI20" s="105"/>
+      <c r="AJ20" s="105"/>
+      <c r="AK20" s="106"/>
+      <c r="AL20" s="21"/>
+      <c r="AM20" s="22"/>
       <c r="AN20" s="5"/>
       <c r="BK20" s="2"/>
     </row>
     <row r="21" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="64"/>
-      <c r="AD21" s="65"/>
-      <c r="AE21" s="127"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="65"/>
-      <c r="AL21" s="27"/>
-      <c r="AM21" s="28"/>
+      <c r="A21" s="118"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="121"/>
+      <c r="U21" s="121"/>
+      <c r="V21" s="121"/>
+      <c r="W21" s="112"/>
+      <c r="X21" s="117"/>
+      <c r="Y21" s="111"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="108"/>
+      <c r="AB21" s="113"/>
+      <c r="AC21" s="105"/>
+      <c r="AD21" s="106"/>
+      <c r="AE21" s="107"/>
+      <c r="AF21" s="105"/>
+      <c r="AG21" s="105"/>
+      <c r="AH21" s="105"/>
+      <c r="AI21" s="105"/>
+      <c r="AJ21" s="105"/>
+      <c r="AK21" s="106"/>
+      <c r="AL21" s="21"/>
+      <c r="AM21" s="22"/>
       <c r="AN21" s="5"/>
       <c r="BK21" s="2"/>
     </row>
     <row r="22" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="127"/>
-      <c r="AF22" s="64"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="27"/>
-      <c r="AM22" s="28"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
+      <c r="V22" s="109"/>
+      <c r="W22" s="116"/>
+      <c r="X22" s="117"/>
+      <c r="Y22" s="111"/>
+      <c r="Z22" s="112"/>
+      <c r="AA22" s="108"/>
+      <c r="AB22" s="113"/>
+      <c r="AC22" s="105"/>
+      <c r="AD22" s="106"/>
+      <c r="AE22" s="107"/>
+      <c r="AF22" s="105"/>
+      <c r="AG22" s="105"/>
+      <c r="AH22" s="105"/>
+      <c r="AI22" s="105"/>
+      <c r="AJ22" s="105"/>
+      <c r="AK22" s="106"/>
+      <c r="AL22" s="21"/>
+      <c r="AM22" s="22"/>
       <c r="AN22" s="5"/>
       <c r="BK22" s="2"/>
     </row>
     <row r="23" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="59"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="127"/>
-      <c r="AF23" s="64"/>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="65"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="28"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="109"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="109"/>
+      <c r="L23" s="109"/>
+      <c r="M23" s="109"/>
+      <c r="N23" s="109"/>
+      <c r="O23" s="109"/>
+      <c r="P23" s="109"/>
+      <c r="Q23" s="109"/>
+      <c r="R23" s="109"/>
+      <c r="S23" s="109"/>
+      <c r="T23" s="109"/>
+      <c r="U23" s="109"/>
+      <c r="V23" s="109"/>
+      <c r="W23" s="116"/>
+      <c r="X23" s="117"/>
+      <c r="Y23" s="111"/>
+      <c r="Z23" s="112"/>
+      <c r="AA23" s="108"/>
+      <c r="AB23" s="113"/>
+      <c r="AC23" s="105"/>
+      <c r="AD23" s="106"/>
+      <c r="AE23" s="107"/>
+      <c r="AF23" s="105"/>
+      <c r="AG23" s="105"/>
+      <c r="AH23" s="105"/>
+      <c r="AI23" s="105"/>
+      <c r="AJ23" s="105"/>
+      <c r="AK23" s="106"/>
+      <c r="AL23" s="21"/>
+      <c r="AM23" s="22"/>
       <c r="AN23" s="5"/>
       <c r="BK23" s="2"/>
     </row>
     <row r="24" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="59"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="34"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="127"/>
-      <c r="AF24" s="64"/>
-      <c r="AG24" s="64"/>
-      <c r="AH24" s="64"/>
-      <c r="AI24" s="64"/>
-      <c r="AJ24" s="64"/>
-      <c r="AK24" s="65"/>
-      <c r="AL24" s="27"/>
-      <c r="AM24" s="28"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="109"/>
+      <c r="K24" s="109"/>
+      <c r="L24" s="109"/>
+      <c r="M24" s="109"/>
+      <c r="N24" s="109"/>
+      <c r="O24" s="109"/>
+      <c r="P24" s="109"/>
+      <c r="Q24" s="109"/>
+      <c r="R24" s="109"/>
+      <c r="S24" s="109"/>
+      <c r="T24" s="109"/>
+      <c r="U24" s="109"/>
+      <c r="V24" s="109"/>
+      <c r="W24" s="116"/>
+      <c r="X24" s="117"/>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="112"/>
+      <c r="AA24" s="108"/>
+      <c r="AB24" s="113"/>
+      <c r="AC24" s="105"/>
+      <c r="AD24" s="106"/>
+      <c r="AE24" s="107"/>
+      <c r="AF24" s="105"/>
+      <c r="AG24" s="105"/>
+      <c r="AH24" s="105"/>
+      <c r="AI24" s="105"/>
+      <c r="AJ24" s="105"/>
+      <c r="AK24" s="106"/>
+      <c r="AL24" s="21"/>
+      <c r="AM24" s="22"/>
       <c r="AN24" s="5"/>
       <c r="BK24" s="2"/>
     </row>
     <row r="25" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="59"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="65"/>
-      <c r="AE25" s="127"/>
-      <c r="AF25" s="64"/>
-      <c r="AG25" s="64"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="64"/>
-      <c r="AJ25" s="64"/>
-      <c r="AK25" s="65"/>
-      <c r="AL25" s="27"/>
-      <c r="AM25" s="28"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="109"/>
+      <c r="S25" s="109"/>
+      <c r="T25" s="109"/>
+      <c r="U25" s="109"/>
+      <c r="V25" s="109"/>
+      <c r="W25" s="116"/>
+      <c r="X25" s="117"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="112"/>
+      <c r="AA25" s="108"/>
+      <c r="AB25" s="113"/>
+      <c r="AC25" s="105"/>
+      <c r="AD25" s="106"/>
+      <c r="AE25" s="107"/>
+      <c r="AF25" s="105"/>
+      <c r="AG25" s="105"/>
+      <c r="AH25" s="105"/>
+      <c r="AI25" s="105"/>
+      <c r="AJ25" s="105"/>
+      <c r="AK25" s="106"/>
+      <c r="AL25" s="21"/>
+      <c r="AM25" s="22"/>
       <c r="AN25" s="5"/>
       <c r="BK25" s="2"/>
     </row>
     <row r="26" spans="1:63" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="29"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="38"/>
-      <c r="AC26" s="64"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="127"/>
-      <c r="AF26" s="64"/>
-      <c r="AG26" s="64"/>
-      <c r="AH26" s="64"/>
-      <c r="AI26" s="64"/>
-      <c r="AJ26" s="64"/>
-      <c r="AK26" s="65"/>
-      <c r="AL26" s="27"/>
-      <c r="AM26" s="28"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="114"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="123"/>
+      <c r="L26" s="123"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123"/>
+      <c r="R26" s="123"/>
+      <c r="S26" s="123"/>
+      <c r="T26" s="123"/>
+      <c r="U26" s="123"/>
+      <c r="V26" s="123"/>
+      <c r="W26" s="124"/>
+      <c r="X26" s="125"/>
+      <c r="Y26" s="126"/>
+      <c r="Z26" s="127"/>
+      <c r="AA26" s="128"/>
+      <c r="AB26" s="129"/>
+      <c r="AC26" s="105"/>
+      <c r="AD26" s="106"/>
+      <c r="AE26" s="107"/>
+      <c r="AF26" s="105"/>
+      <c r="AG26" s="105"/>
+      <c r="AH26" s="105"/>
+      <c r="AI26" s="105"/>
+      <c r="AJ26" s="105"/>
+      <c r="AK26" s="106"/>
+      <c r="AL26" s="21"/>
+      <c r="AM26" s="22"/>
       <c r="AN26" s="5"/>
       <c r="BK26" s="2"/>
     </row>
@@ -3040,6 +3119,63 @@
     <row r="29" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q4:S6"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="T4:AK4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="R2:AH2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C4:P4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="C16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="AC16:AD17"/>
+    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AF5:AF6"/>
     <mergeCell ref="AC26:AD26"/>
     <mergeCell ref="AE18:AK18"/>
     <mergeCell ref="AE19:AK19"/>
@@ -3056,63 +3192,6 @@
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="C16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="AC16:AD17"/>
-    <mergeCell ref="AE16:AK17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="C4:P4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="R2:AH2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q4:S6"/>
-    <mergeCell ref="AD5:AE5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Отчёт.xlsx
+++ b/Отчёт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Projects\СОЭЗ\Telegram\form_kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672218A0-6752-45B3-905F-4D43A81A1D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD3EAF3-9FAB-43E7-BCF6-5EEE5F14B197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{896FA051-009E-4318-B742-8FCF3A1B02A5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="113">
   <si>
     <t>недолив</t>
   </si>
@@ -115,9 +115,6 @@
     <t>технол. брак (ЛПД)</t>
   </si>
   <si>
-    <t>Дата:  ______________________________  2025 г.</t>
-  </si>
-  <si>
     <t>ОКОНЧАТЕЛЬНЫЙ БРАК, шт.</t>
   </si>
   <si>
@@ -385,7 +382,7 @@
     <t>Наименование_отливки</t>
   </si>
   <si>
-    <t>,</t>
+    <t xml:space="preserve">Дата: </t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1229,6 +1226,270 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1238,278 +1499,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1860,139 +1854,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="73"/>
-      <c r="AK1" s="73"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
       <c r="AL1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="L2" s="60" t="s">
+      <c r="A2" s="128" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="L2" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
+      <c r="U2" s="128"/>
+      <c r="V2" s="128"/>
+      <c r="W2" s="128"/>
+      <c r="X2" s="128"/>
+      <c r="Y2" s="128"/>
+      <c r="Z2" s="128"/>
+      <c r="AA2" s="128"/>
+      <c r="AB2" s="128"/>
+      <c r="AC2" s="128"/>
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="128"/>
+      <c r="AG2" s="128"/>
+      <c r="AH2" s="128"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:38" s="7" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="83" t="s">
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="84"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="63" t="s">
+      <c r="R4" s="72"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="64"/>
-      <c r="AD4" s="64"/>
-      <c r="AE4" s="64"/>
-      <c r="AF4" s="64"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="64"/>
-      <c r="AI4" s="64"/>
-      <c r="AJ4" s="64"/>
-      <c r="AK4" s="65"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="83"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="84"/>
       <c r="AL4" s="6"/>
     </row>
     <row r="5" spans="1:38" s="9" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66" t="s">
+      <c r="A5" s="88"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="92" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="68" t="s">
@@ -2031,116 +2023,116 @@
       <c r="O5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="82" t="s">
+      <c r="P5" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="88"/>
-      <c r="T5" s="74" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="39" t="s">
+      <c r="V5" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="39" t="s">
+      <c r="W5" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="39" t="s">
+      <c r="X5" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="X5" s="39" t="s">
+      <c r="Y5" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="61" t="s">
+      <c r="Z5" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="61" t="s">
+      <c r="AA5" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="AA5" s="39" t="s">
+      <c r="AB5" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="39" t="s">
+      <c r="AC5" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="69" t="s">
+      <c r="AD5" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE5" s="61"/>
-      <c r="AF5" s="71" t="s">
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="122" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG5" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH5" s="39" t="s">
+      <c r="AH5" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI5" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="AI5" s="39" t="s">
+      <c r="AJ5" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AJ5" s="39" t="s">
+      <c r="AK5" s="90" t="s">
         <v>29</v>
-      </c>
-      <c r="AK5" s="78" t="s">
-        <v>30</v>
       </c>
       <c r="AL5" s="8"/>
     </row>
     <row r="6" spans="1:38" s="9" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="89"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="70"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="86"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="119"/>
+      <c r="Z6" s="119"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="121"/>
       <c r="AD6" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="AE6" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="79"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="70"/>
       <c r="AL6" s="8"/>
     </row>
     <row r="7" spans="1:38" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
@@ -2156,64 +2148,64 @@
       <c r="N7" s="27"/>
       <c r="O7" s="27"/>
       <c r="P7" s="29"/>
-      <c r="Q7" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="R7" s="58"/>
-      <c r="S7" s="59"/>
+      <c r="Q7" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7" s="98"/>
+      <c r="S7" s="99"/>
       <c r="T7" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="U7" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="U7" s="32" t="s">
+      <c r="V7" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="V7" s="32" t="s">
+      <c r="W7" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="W7" s="32" t="s">
+      <c r="X7" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="X7" s="32" t="s">
+      <c r="Y7" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="Y7" s="32" t="s">
+      <c r="Z7" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="Z7" s="32" t="s">
+      <c r="AA7" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="AA7" s="32" t="s">
+      <c r="AB7" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="AB7" s="32" t="s">
+      <c r="AC7" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="AC7" s="32" t="s">
+      <c r="AD7" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE7" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF7" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="AD7" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE7" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF7" s="32" t="s">
+      <c r="AG7" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="AG7" s="32" t="s">
+      <c r="AH7" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="AH7" s="32" t="s">
+      <c r="AI7" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="AI7" s="32" t="s">
+      <c r="AJ7" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="AJ7" s="32" t="s">
+      <c r="AK7" s="32" t="s">
         <v>87</v>
-      </c>
-      <c r="AK7" s="32" t="s">
-        <v>88</v>
       </c>
       <c r="AL7" s="14"/>
     </row>
@@ -2234,27 +2226,27 @@
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="13"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="100"/>
-      <c r="T8" s="93"/>
-      <c r="U8" s="93"/>
-      <c r="V8" s="93"/>
-      <c r="W8" s="93"/>
-      <c r="X8" s="93"/>
-      <c r="Y8" s="93"/>
-      <c r="Z8" s="93"/>
-      <c r="AA8" s="93"/>
-      <c r="AB8" s="93"/>
-      <c r="AC8" s="93"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="101"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="37"/>
       <c r="AD8" s="32"/>
-      <c r="AE8" s="93"/>
-      <c r="AF8" s="93"/>
-      <c r="AG8" s="93"/>
-      <c r="AH8" s="93"/>
-      <c r="AI8" s="93"/>
-      <c r="AJ8" s="93"/>
-      <c r="AK8" s="94"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="37"/>
+      <c r="AG8" s="37"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="37"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="38"/>
       <c r="AL8" s="14"/>
     </row>
     <row r="9" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2274,27 +2266,27 @@
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="100"/>
-      <c r="T9" s="94"/>
-      <c r="U9" s="94"/>
-      <c r="V9" s="94"/>
-      <c r="W9" s="94"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="94"/>
-      <c r="Z9" s="94"/>
-      <c r="AA9" s="94"/>
-      <c r="AB9" s="94"/>
-      <c r="AC9" s="94"/>
-      <c r="AD9" s="94"/>
-      <c r="AE9" s="94"/>
-      <c r="AF9" s="94"/>
-      <c r="AG9" s="95"/>
-      <c r="AH9" s="94"/>
-      <c r="AI9" s="94"/>
-      <c r="AJ9" s="92"/>
-      <c r="AK9" s="94"/>
+      <c r="Q9" s="100"/>
+      <c r="R9" s="101"/>
+      <c r="S9" s="102"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="38"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="38"/>
       <c r="AL9" s="14"/>
     </row>
     <row r="10" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2314,27 +2306,27 @@
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="99"/>
-      <c r="S10" s="100"/>
-      <c r="T10" s="94"/>
-      <c r="U10" s="94"/>
-      <c r="V10" s="94"/>
-      <c r="W10" s="94"/>
-      <c r="X10" s="94"/>
-      <c r="Y10" s="94"/>
-      <c r="Z10" s="94"/>
-      <c r="AA10" s="94"/>
-      <c r="AB10" s="94"/>
-      <c r="AC10" s="94"/>
-      <c r="AD10" s="94"/>
-      <c r="AE10" s="94"/>
-      <c r="AF10" s="94"/>
-      <c r="AG10" s="95"/>
-      <c r="AH10" s="94"/>
-      <c r="AI10" s="94"/>
-      <c r="AJ10" s="92"/>
-      <c r="AK10" s="94"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="36"/>
+      <c r="AK10" s="38"/>
       <c r="AL10" s="14"/>
     </row>
     <row r="11" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2354,27 +2346,27 @@
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
       <c r="P11" s="13"/>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="103"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="94"/>
-      <c r="Z11" s="94"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="96"/>
-      <c r="AE11" s="96"/>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="97"/>
-      <c r="AH11" s="94"/>
-      <c r="AI11" s="94"/>
-      <c r="AJ11" s="92"/>
-      <c r="AK11" s="94"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="104"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="38"/>
       <c r="AL11" s="14"/>
     </row>
     <row r="12" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2394,27 +2386,27 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="13"/>
-      <c r="Q12" s="104"/>
-      <c r="R12" s="104"/>
-      <c r="S12" s="104"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94"/>
-      <c r="W12" s="94"/>
-      <c r="X12" s="94"/>
-      <c r="Y12" s="94"/>
-      <c r="Z12" s="94"/>
-      <c r="AA12" s="94"/>
-      <c r="AB12" s="94"/>
-      <c r="AC12" s="94"/>
-      <c r="AD12" s="94"/>
-      <c r="AE12" s="94"/>
-      <c r="AF12" s="94"/>
-      <c r="AG12" s="95"/>
-      <c r="AH12" s="94"/>
-      <c r="AI12" s="94"/>
-      <c r="AJ12" s="92"/>
-      <c r="AK12" s="94"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="106"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="38"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="38"/>
       <c r="AL12" s="14"/>
     </row>
     <row r="13" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2434,27 +2426,27 @@
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
       <c r="P13" s="13"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="102"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="96"/>
-      <c r="Y13" s="94"/>
-      <c r="Z13" s="94"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="96"/>
-      <c r="AE13" s="96"/>
-      <c r="AF13" s="96"/>
-      <c r="AG13" s="97"/>
-      <c r="AH13" s="94"/>
-      <c r="AI13" s="94"/>
-      <c r="AJ13" s="92"/>
-      <c r="AK13" s="94"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="105"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="41"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="38"/>
       <c r="AL13" s="14"/>
     </row>
     <row r="14" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2474,36 +2466,36 @@
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="13"/>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="104"/>
-      <c r="S14" s="104"/>
-      <c r="T14" s="94"/>
-      <c r="U14" s="94"/>
-      <c r="V14" s="94"/>
-      <c r="W14" s="94"/>
-      <c r="X14" s="94"/>
-      <c r="Y14" s="94"/>
-      <c r="Z14" s="94"/>
-      <c r="AA14" s="94"/>
-      <c r="AB14" s="94"/>
-      <c r="AC14" s="94"/>
-      <c r="AD14" s="94"/>
-      <c r="AE14" s="94"/>
-      <c r="AF14" s="94"/>
-      <c r="AG14" s="95"/>
-      <c r="AH14" s="94"/>
-      <c r="AI14" s="94"/>
-      <c r="AJ14" s="92"/>
-      <c r="AK14" s="94"/>
+      <c r="Q14" s="106"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="38"/>
+      <c r="AD14" s="38"/>
+      <c r="AE14" s="38"/>
+      <c r="AF14" s="38"/>
+      <c r="AG14" s="39"/>
+      <c r="AH14" s="38"/>
+      <c r="AI14" s="38"/>
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="38"/>
       <c r="AL14" s="14"/>
     </row>
     <row r="15" spans="1:38" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="17"/>
@@ -2526,146 +2518,146 @@
       <c r="AJ15" s="5"/>
     </row>
     <row r="16" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="109"/>
+      <c r="Y16" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
-      <c r="U16" s="42"/>
-      <c r="V16" s="42"/>
-      <c r="W16" s="42"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="47" t="s">
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="AD16" s="48"/>
-      <c r="AE16" s="47" t="s">
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="51"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="51"/>
-      <c r="AI16" s="51"/>
-      <c r="AJ16" s="51"/>
-      <c r="AK16" s="48"/>
+      <c r="AF16" s="117"/>
+      <c r="AG16" s="117"/>
+      <c r="AH16" s="117"/>
+      <c r="AI16" s="117"/>
+      <c r="AJ16" s="117"/>
+      <c r="AK16" s="114"/>
     </row>
     <row r="17" spans="1:63" ht="135.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
-      <c r="B17" s="56"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="96"/>
       <c r="C17" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="25" t="s">
+      <c r="F17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="G17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="H17" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="I17" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="J17" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="J17" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="25" t="s">
+      <c r="L17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="M17" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="N17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="O17" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="O17" s="25" t="s">
+      <c r="P17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="P17" s="25" t="s">
+      <c r="Q17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="R17" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="25" t="s">
+      <c r="S17" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="T17" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="T17" s="25" t="s">
+      <c r="U17" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="U17" s="25" t="s">
+      <c r="V17" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="V17" s="25" t="s">
+      <c r="W17" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="W17" s="25" t="s">
+      <c r="X17" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="X17" s="33" t="s">
-        <v>65</v>
-      </c>
       <c r="Y17" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z17" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="AA17" s="25" t="s">
-        <v>55</v>
-      </c>
       <c r="AB17" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC17" s="49"/>
-      <c r="AD17" s="50"/>
-      <c r="AE17" s="49"/>
-      <c r="AF17" s="52"/>
-      <c r="AG17" s="52"/>
-      <c r="AH17" s="52"/>
-      <c r="AI17" s="52"/>
-      <c r="AJ17" s="52"/>
-      <c r="AK17" s="50"/>
+        <v>64</v>
+      </c>
+      <c r="AC17" s="115"/>
+      <c r="AD17" s="116"/>
+      <c r="AE17" s="115"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="118"/>
+      <c r="AH17" s="118"/>
+      <c r="AI17" s="118"/>
+      <c r="AJ17" s="118"/>
+      <c r="AK17" s="116"/>
       <c r="AL17" s="18"/>
       <c r="AM17" s="19"/>
       <c r="AN17" s="5"/>
@@ -2673,442 +2665,442 @@
     </row>
     <row r="18" spans="1:63" ht="99" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="L18" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="M18" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="O18" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="P18" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q18" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="R18" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="S18" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="32" t="s">
+      <c r="T18" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="U18" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="V18" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="W18" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="X18" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y18" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z18" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA18" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="125"/>
+      <c r="AD18" s="126"/>
+      <c r="AE18" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="K18" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="M18" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="N18" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="P18" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q18" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="R18" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="S18" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="T18" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="U18" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="V18" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="W18" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="X18" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y18" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z18" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA18" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="37"/>
-      <c r="AD18" s="38"/>
-      <c r="AE18" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF18" s="37"/>
-      <c r="AG18" s="37"/>
-      <c r="AH18" s="37"/>
-      <c r="AI18" s="37"/>
-      <c r="AJ18" s="37"/>
-      <c r="AK18" s="38"/>
+      <c r="AF18" s="125"/>
+      <c r="AG18" s="125"/>
+      <c r="AH18" s="125"/>
+      <c r="AI18" s="125"/>
+      <c r="AJ18" s="125"/>
+      <c r="AK18" s="126"/>
       <c r="AL18" s="21"/>
       <c r="AM18" s="22"/>
       <c r="AN18" s="5"/>
       <c r="BK18" s="2"/>
     </row>
     <row r="19" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="108"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="109"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="32"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="109"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
       <c r="M19" s="32"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="109"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="109"/>
-      <c r="W19" s="109"/>
-      <c r="X19" s="110"/>
-      <c r="Y19" s="111"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="105"/>
-      <c r="AD19" s="106"/>
-      <c r="AE19" s="107"/>
-      <c r="AF19" s="105"/>
-      <c r="AG19" s="105"/>
-      <c r="AH19" s="105"/>
-      <c r="AI19" s="105"/>
-      <c r="AJ19" s="105"/>
-      <c r="AK19" s="106"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="45"/>
+      <c r="Z19" s="46"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="47"/>
+      <c r="AC19" s="64"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="127"/>
+      <c r="AF19" s="64"/>
+      <c r="AG19" s="64"/>
+      <c r="AH19" s="64"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="64"/>
+      <c r="AK19" s="65"/>
       <c r="AL19" s="21"/>
       <c r="AM19" s="22"/>
       <c r="AN19" s="5"/>
       <c r="BK19" s="2"/>
     </row>
     <row r="20" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="108"/>
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="109"/>
-      <c r="R20" s="109"/>
-      <c r="S20" s="109"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="109"/>
-      <c r="V20" s="109"/>
-      <c r="W20" s="116"/>
-      <c r="X20" s="117"/>
-      <c r="Y20" s="111"/>
-      <c r="Z20" s="112"/>
-      <c r="AA20" s="108"/>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="105"/>
-      <c r="AD20" s="106"/>
-      <c r="AE20" s="107"/>
-      <c r="AF20" s="105"/>
-      <c r="AG20" s="105"/>
-      <c r="AH20" s="105"/>
-      <c r="AI20" s="105"/>
-      <c r="AJ20" s="105"/>
-      <c r="AK20" s="106"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="45"/>
+      <c r="Z20" s="46"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="47"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="65"/>
+      <c r="AE20" s="127"/>
+      <c r="AF20" s="64"/>
+      <c r="AG20" s="64"/>
+      <c r="AH20" s="64"/>
+      <c r="AI20" s="64"/>
+      <c r="AJ20" s="64"/>
+      <c r="AK20" s="65"/>
       <c r="AL20" s="21"/>
       <c r="AM20" s="22"/>
       <c r="AN20" s="5"/>
       <c r="BK20" s="2"/>
     </row>
     <row r="21" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="118"/>
-      <c r="B21" s="119"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="121"/>
-      <c r="S21" s="121"/>
-      <c r="T21" s="121"/>
-      <c r="U21" s="121"/>
-      <c r="V21" s="121"/>
-      <c r="W21" s="112"/>
-      <c r="X21" s="117"/>
-      <c r="Y21" s="111"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="108"/>
-      <c r="AB21" s="113"/>
-      <c r="AC21" s="105"/>
-      <c r="AD21" s="106"/>
-      <c r="AE21" s="107"/>
-      <c r="AF21" s="105"/>
-      <c r="AG21" s="105"/>
-      <c r="AH21" s="105"/>
-      <c r="AI21" s="105"/>
-      <c r="AJ21" s="105"/>
-      <c r="AK21" s="106"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="51"/>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="46"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="47"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="65"/>
+      <c r="AE21" s="127"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="64"/>
+      <c r="AJ21" s="64"/>
+      <c r="AK21" s="65"/>
       <c r="AL21" s="21"/>
       <c r="AM21" s="22"/>
       <c r="AN21" s="5"/>
       <c r="BK21" s="2"/>
     </row>
     <row r="22" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="108"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="109"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="109"/>
-      <c r="V22" s="109"/>
-      <c r="W22" s="116"/>
-      <c r="X22" s="117"/>
-      <c r="Y22" s="111"/>
-      <c r="Z22" s="112"/>
-      <c r="AA22" s="108"/>
-      <c r="AB22" s="113"/>
-      <c r="AC22" s="105"/>
-      <c r="AD22" s="106"/>
-      <c r="AE22" s="107"/>
-      <c r="AF22" s="105"/>
-      <c r="AG22" s="105"/>
-      <c r="AH22" s="105"/>
-      <c r="AI22" s="105"/>
-      <c r="AJ22" s="105"/>
-      <c r="AK22" s="106"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
+      <c r="W22" s="50"/>
+      <c r="X22" s="51"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="46"/>
+      <c r="AA22" s="42"/>
+      <c r="AB22" s="47"/>
+      <c r="AC22" s="64"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="127"/>
+      <c r="AF22" s="64"/>
+      <c r="AG22" s="64"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="65"/>
       <c r="AL22" s="21"/>
       <c r="AM22" s="22"/>
       <c r="AN22" s="5"/>
       <c r="BK22" s="2"/>
     </row>
     <row r="23" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="109"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="109"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="109"/>
-      <c r="O23" s="109"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="109"/>
-      <c r="R23" s="109"/>
-      <c r="S23" s="109"/>
-      <c r="T23" s="109"/>
-      <c r="U23" s="109"/>
-      <c r="V23" s="109"/>
-      <c r="W23" s="116"/>
-      <c r="X23" s="117"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="113"/>
-      <c r="AC23" s="105"/>
-      <c r="AD23" s="106"/>
-      <c r="AE23" s="107"/>
-      <c r="AF23" s="105"/>
-      <c r="AG23" s="105"/>
-      <c r="AH23" s="105"/>
-      <c r="AI23" s="105"/>
-      <c r="AJ23" s="105"/>
-      <c r="AK23" s="106"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="51"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="47"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="127"/>
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="65"/>
       <c r="AL23" s="21"/>
       <c r="AM23" s="22"/>
       <c r="AN23" s="5"/>
       <c r="BK23" s="2"/>
     </row>
     <row r="24" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="108"/>
-      <c r="B24" s="114"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="109"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="109"/>
-      <c r="O24" s="109"/>
-      <c r="P24" s="109"/>
-      <c r="Q24" s="109"/>
-      <c r="R24" s="109"/>
-      <c r="S24" s="109"/>
-      <c r="T24" s="109"/>
-      <c r="U24" s="109"/>
-      <c r="V24" s="109"/>
-      <c r="W24" s="116"/>
-      <c r="X24" s="117"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="112"/>
-      <c r="AA24" s="108"/>
-      <c r="AB24" s="113"/>
-      <c r="AC24" s="105"/>
-      <c r="AD24" s="106"/>
-      <c r="AE24" s="107"/>
-      <c r="AF24" s="105"/>
-      <c r="AG24" s="105"/>
-      <c r="AH24" s="105"/>
-      <c r="AI24" s="105"/>
-      <c r="AJ24" s="105"/>
-      <c r="AK24" s="106"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="51"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="47"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="127"/>
+      <c r="AF24" s="64"/>
+      <c r="AG24" s="64"/>
+      <c r="AH24" s="64"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="64"/>
+      <c r="AK24" s="65"/>
       <c r="AL24" s="21"/>
       <c r="AM24" s="22"/>
       <c r="AN24" s="5"/>
       <c r="BK24" s="2"/>
     </row>
     <row r="25" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="108"/>
-      <c r="B25" s="114"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="109"/>
-      <c r="R25" s="109"/>
-      <c r="S25" s="109"/>
-      <c r="T25" s="109"/>
-      <c r="U25" s="109"/>
-      <c r="V25" s="109"/>
-      <c r="W25" s="116"/>
-      <c r="X25" s="117"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="112"/>
-      <c r="AA25" s="108"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="105"/>
-      <c r="AD25" s="106"/>
-      <c r="AE25" s="107"/>
-      <c r="AF25" s="105"/>
-      <c r="AG25" s="105"/>
-      <c r="AH25" s="105"/>
-      <c r="AI25" s="105"/>
-      <c r="AJ25" s="105"/>
-      <c r="AK25" s="106"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="51"/>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="42"/>
+      <c r="AB25" s="47"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="65"/>
+      <c r="AE25" s="127"/>
+      <c r="AF25" s="64"/>
+      <c r="AG25" s="64"/>
+      <c r="AH25" s="64"/>
+      <c r="AI25" s="64"/>
+      <c r="AJ25" s="64"/>
+      <c r="AK25" s="65"/>
       <c r="AL25" s="21"/>
       <c r="AM25" s="22"/>
       <c r="AN25" s="5"/>
       <c r="BK25" s="2"/>
     </row>
     <row r="26" spans="1:63" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="108"/>
-      <c r="B26" s="114"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="123"/>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123"/>
-      <c r="O26" s="123"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="123"/>
-      <c r="R26" s="123"/>
-      <c r="S26" s="123"/>
-      <c r="T26" s="123"/>
-      <c r="U26" s="123"/>
-      <c r="V26" s="123"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="125"/>
-      <c r="Y26" s="126"/>
-      <c r="Z26" s="127"/>
-      <c r="AA26" s="128"/>
-      <c r="AB26" s="129"/>
-      <c r="AC26" s="105"/>
-      <c r="AD26" s="106"/>
-      <c r="AE26" s="107"/>
-      <c r="AF26" s="105"/>
-      <c r="AG26" s="105"/>
-      <c r="AH26" s="105"/>
-      <c r="AI26" s="105"/>
-      <c r="AJ26" s="105"/>
-      <c r="AK26" s="106"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="59"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="62"/>
+      <c r="AB26" s="63"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="65"/>
+      <c r="AE26" s="127"/>
+      <c r="AF26" s="64"/>
+      <c r="AG26" s="64"/>
+      <c r="AH26" s="64"/>
+      <c r="AI26" s="64"/>
+      <c r="AJ26" s="64"/>
+      <c r="AK26" s="65"/>
       <c r="AL26" s="21"/>
       <c r="AM26" s="22"/>
       <c r="AN26" s="5"/>
@@ -3118,64 +3110,8 @@
     <row r="28" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q4:S6"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="R2:AH2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C4:P4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="C16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="AC16:AD17"/>
-    <mergeCell ref="AE16:AK17"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AF5:AF6"/>
+  <mergeCells count="72">
+    <mergeCell ref="L2:AH2"/>
     <mergeCell ref="AC26:AD26"/>
     <mergeCell ref="AE18:AK18"/>
     <mergeCell ref="AE19:AK19"/>
@@ -3192,6 +3128,61 @@
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="C16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="AC16:AD17"/>
+    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="T4:AK4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q4:S6"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="C4:P4"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Отчёт.xlsx
+++ b/Отчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Projects\СОЭЗ\Telegram\form_kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD3EAF3-9FAB-43E7-BCF6-5EEE5F14B197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2522F03F-8227-4210-A124-F2FCC3E0A33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{896FA051-009E-4318-B742-8FCF3A1B02A5}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{896FA051-009E-4318-B742-8FCF3A1B02A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -389,7 +389,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,13 +477,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -492,9 +485,24 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -1153,7 +1161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1174,14 +1182,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1226,94 +1232,22 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1361,24 +1295,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1392,22 +1341,61 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1418,78 +1406,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1499,11 +1415,98 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1854,651 +1857,672 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="64"/>
+      <c r="AG1" s="64"/>
+      <c r="AH1" s="64"/>
+      <c r="AI1" s="64"/>
+      <c r="AJ1" s="64"/>
+      <c r="AK1" s="64"/>
       <c r="AL1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="L2" s="128" t="s">
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="L2" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="128"/>
-      <c r="T2" s="128"/>
-      <c r="U2" s="128"/>
-      <c r="V2" s="128"/>
-      <c r="W2" s="128"/>
-      <c r="X2" s="128"/>
-      <c r="Y2" s="128"/>
-      <c r="Z2" s="128"/>
-      <c r="AA2" s="128"/>
-      <c r="AB2" s="128"/>
-      <c r="AC2" s="128"/>
-      <c r="AD2" s="128"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="128"/>
-      <c r="AG2" s="128"/>
-      <c r="AH2" s="128"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70"/>
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70"/>
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
     <row r="3" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:38" s="7" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="71" t="s">
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="72"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="82" t="s">
+      <c r="R4" s="46"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="83"/>
-      <c r="Y4" s="83"/>
-      <c r="Z4" s="83"/>
-      <c r="AA4" s="83"/>
-      <c r="AB4" s="83"/>
-      <c r="AC4" s="83"/>
-      <c r="AD4" s="83"/>
-      <c r="AE4" s="83"/>
-      <c r="AF4" s="83"/>
-      <c r="AG4" s="83"/>
-      <c r="AH4" s="83"/>
-      <c r="AI4" s="83"/>
-      <c r="AJ4" s="83"/>
-      <c r="AK4" s="84"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="56"/>
+      <c r="AI4" s="56"/>
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="57"/>
       <c r="AL4" s="6"/>
     </row>
     <row r="5" spans="1:38" s="9" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="88"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="92" t="s">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="68" t="s">
+      <c r="K5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="68" t="s">
+      <c r="N5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="68" t="s">
+      <c r="O5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="85" t="s">
+      <c r="Q5" s="48"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="66" t="s">
+      <c r="U5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="V5" s="66" t="s">
+      <c r="V5" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="W5" s="66" t="s">
+      <c r="W5" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="X5" s="66" t="s">
+      <c r="X5" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="Y5" s="80" t="s">
+      <c r="Y5" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="Z5" s="80" t="s">
+      <c r="Z5" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="AA5" s="66" t="s">
+      <c r="AA5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="AB5" s="66" t="s">
+      <c r="AB5" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="AC5" s="120" t="s">
+      <c r="AC5" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" s="80"/>
-      <c r="AF5" s="122" t="s">
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="AG5" s="66" t="s">
+      <c r="AG5" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="AH5" s="66" t="s">
+      <c r="AH5" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="AI5" s="66" t="s">
+      <c r="AI5" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AJ5" s="66" t="s">
+      <c r="AJ5" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="AK5" s="90" t="s">
+      <c r="AK5" s="69" t="s">
         <v>29</v>
       </c>
       <c r="AL5" s="8"/>
     </row>
     <row r="6" spans="1:38" s="9" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="86"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="119"/>
-      <c r="Z6" s="119"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="121"/>
-      <c r="AD6" s="31" t="s">
+      <c r="A6" s="68"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="83"/>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="85"/>
+      <c r="AD6" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AE6" s="31" t="s">
+      <c r="AE6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="AF6" s="123"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="70"/>
+      <c r="AF6" s="87"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="44"/>
       <c r="AL6" s="8"/>
     </row>
     <row r="7" spans="1:38" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="97" t="s">
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="R7" s="98"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="32" t="s">
+      <c r="R7" s="90"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="U7" s="32" t="s">
+      <c r="U7" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="V7" s="32" t="s">
+      <c r="V7" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="W7" s="32" t="s">
+      <c r="W7" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="X7" s="32" t="s">
+      <c r="X7" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="Y7" s="32" t="s">
+      <c r="Y7" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="32" t="s">
+      <c r="Z7" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="AA7" s="32" t="s">
+      <c r="AA7" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="AB7" s="32" t="s">
+      <c r="AB7" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="AC7" s="32" t="s">
+      <c r="AC7" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="AD7" s="32" t="s">
+      <c r="AD7" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="AE7" s="32" t="s">
+      <c r="AE7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="AF7" s="32" t="s">
+      <c r="AF7" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="AG7" s="32" t="s">
+      <c r="AG7" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="AH7" s="32" t="s">
+      <c r="AH7" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="AI7" s="32" t="s">
+      <c r="AI7" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="AJ7" s="32" t="s">
+      <c r="AJ7" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AK7" s="32" t="s">
+      <c r="AK7" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="AL7" s="14"/>
+      <c r="AL7" s="13"/>
     </row>
     <row r="8" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="100"/>
-      <c r="R8" s="101"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="14"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34">
+        <f>Q8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="36"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="101"/>
+      <c r="AE8" s="36"/>
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="36"/>
+      <c r="AH8" s="36"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="36"/>
+      <c r="AK8" s="36"/>
+      <c r="AL8" s="13"/>
     </row>
     <row r="9" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="100"/>
-      <c r="R9" s="101"/>
-      <c r="S9" s="102"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="38"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="38"/>
-      <c r="AJ9" s="36"/>
-      <c r="AK9" s="38"/>
-      <c r="AL9" s="14"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="34">
+        <f t="shared" ref="B9:B14" si="0">Q9</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="36"/>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="102"/>
+      <c r="AH9" s="36"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="103"/>
+      <c r="AK9" s="36"/>
+      <c r="AL9" s="13"/>
     </row>
     <row r="10" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="100"/>
-      <c r="R10" s="101"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="38"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="38"/>
-      <c r="AD10" s="38"/>
-      <c r="AE10" s="38"/>
-      <c r="AF10" s="38"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="38"/>
-      <c r="AI10" s="38"/>
-      <c r="AJ10" s="36"/>
-      <c r="AK10" s="38"/>
-      <c r="AL10" s="14"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="100"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="36"/>
+      <c r="AE10" s="36"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="102"/>
+      <c r="AH10" s="36"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="103"/>
+      <c r="AK10" s="36"/>
+      <c r="AL10" s="13"/>
     </row>
     <row r="11" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="104"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="41"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="36"/>
-      <c r="AK11" s="38"/>
-      <c r="AL11" s="14"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="104"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="106"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="107"/>
+      <c r="V11" s="107"/>
+      <c r="W11" s="107"/>
+      <c r="X11" s="107"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="107"/>
+      <c r="AB11" s="107"/>
+      <c r="AC11" s="107"/>
+      <c r="AD11" s="107"/>
+      <c r="AE11" s="107"/>
+      <c r="AF11" s="107"/>
+      <c r="AG11" s="108"/>
+      <c r="AH11" s="36"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="36"/>
+      <c r="AL11" s="13"/>
     </row>
     <row r="12" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="36"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="14"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="109"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="102"/>
+      <c r="AH12" s="36"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="13"/>
     </row>
     <row r="13" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="105"/>
-      <c r="T13" s="40"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="40"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="40"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="38"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="38"/>
-      <c r="AL13" s="14"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="105"/>
+      <c r="S13" s="106"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="107"/>
+      <c r="V13" s="107"/>
+      <c r="W13" s="107"/>
+      <c r="X13" s="107"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="107"/>
+      <c r="AB13" s="107"/>
+      <c r="AC13" s="107"/>
+      <c r="AD13" s="107"/>
+      <c r="AE13" s="107"/>
+      <c r="AF13" s="107"/>
+      <c r="AG13" s="108"/>
+      <c r="AH13" s="36"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="13"/>
     </row>
     <row r="14" spans="1:38" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="106"/>
-      <c r="R14" s="106"/>
-      <c r="S14" s="106"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="38"/>
-      <c r="AB14" s="38"/>
-      <c r="AC14" s="38"/>
-      <c r="AD14" s="38"/>
-      <c r="AE14" s="38"/>
-      <c r="AF14" s="38"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="38"/>
-      <c r="AI14" s="38"/>
-      <c r="AJ14" s="36"/>
-      <c r="AK14" s="38"/>
-      <c r="AL14" s="14"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="109"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="36"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="102"/>
+      <c r="AH14" s="36"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="36"/>
+      <c r="AL14" s="13"/>
     </row>
     <row r="15" spans="1:38" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="17"/>
+      <c r="S15" s="15"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -2518,591 +2542,591 @@
       <c r="AJ15" s="5"/>
     </row>
     <row r="16" spans="1:38" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="93" t="s">
+      <c r="A16" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="107" t="s">
+      <c r="C16" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="108"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="108"/>
-      <c r="Q16" s="108"/>
-      <c r="R16" s="108"/>
-      <c r="S16" s="108"/>
-      <c r="T16" s="108"/>
-      <c r="U16" s="108"/>
-      <c r="V16" s="108"/>
-      <c r="W16" s="108"/>
-      <c r="X16" s="109"/>
-      <c r="Y16" s="110" t="s">
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="Z16" s="111"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="113" t="s">
+      <c r="Z16" s="75"/>
+      <c r="AA16" s="75"/>
+      <c r="AB16" s="76"/>
+      <c r="AC16" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="113" t="s">
+      <c r="AD16" s="78"/>
+      <c r="AE16" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="117"/>
-      <c r="AG16" s="117"/>
-      <c r="AH16" s="117"/>
-      <c r="AI16" s="117"/>
-      <c r="AJ16" s="117"/>
-      <c r="AK16" s="114"/>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="81"/>
+      <c r="AH16" s="81"/>
+      <c r="AI16" s="81"/>
+      <c r="AJ16" s="81"/>
+      <c r="AK16" s="78"/>
     </row>
     <row r="17" spans="1:63" ht="135.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
-      <c r="B17" s="96"/>
-      <c r="C17" s="24" t="s">
+      <c r="A17" s="61"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="K17" s="25" t="s">
+      <c r="K17" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="L17" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N17" s="25" t="s">
+      <c r="N17" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="25" t="s">
+      <c r="O17" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="25" t="s">
+      <c r="P17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="R17" s="25" t="s">
+      <c r="R17" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="S17" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="T17" s="25" t="s">
+      <c r="T17" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="U17" s="25" t="s">
+      <c r="U17" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="V17" s="25" t="s">
+      <c r="V17" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="W17" s="25" t="s">
+      <c r="W17" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="X17" s="33" t="s">
+      <c r="X17" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="Y17" s="24" t="s">
+      <c r="Y17" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="Z17" s="25" t="s">
+      <c r="Z17" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AA17" s="25" t="s">
+      <c r="AA17" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="AB17" s="26" t="s">
+      <c r="AB17" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="AC17" s="115"/>
-      <c r="AD17" s="116"/>
-      <c r="AE17" s="115"/>
-      <c r="AF17" s="118"/>
-      <c r="AG17" s="118"/>
-      <c r="AH17" s="118"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="118"/>
-      <c r="AK17" s="116"/>
-      <c r="AL17" s="18"/>
-      <c r="AM17" s="19"/>
+      <c r="AC17" s="79"/>
+      <c r="AD17" s="80"/>
+      <c r="AE17" s="79"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="80"/>
+      <c r="AL17" s="16"/>
+      <c r="AM17" s="17"/>
       <c r="AN17" s="5"/>
       <c r="BK17" s="2"/>
     </row>
     <row r="18" spans="1:63" ht="99" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="K18" s="32" t="s">
+      <c r="K18" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="32" t="s">
+      <c r="L18" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="N18" s="32" t="s">
+      <c r="N18" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="O18" s="32" t="s">
+      <c r="O18" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="P18" s="32" t="s">
+      <c r="P18" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="Q18" s="32" t="s">
+      <c r="Q18" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="R18" s="32" t="s">
+      <c r="R18" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="S18" s="32" t="s">
+      <c r="S18" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="T18" s="32" t="s">
+      <c r="T18" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="U18" s="32" t="s">
+      <c r="U18" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="V18" s="32" t="s">
+      <c r="V18" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="W18" s="32" t="s">
+      <c r="W18" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="X18" s="34" t="s">
+      <c r="X18" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="Y18" s="35" t="s">
+      <c r="Y18" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="Z18" s="32" t="s">
+      <c r="Z18" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="AA18" s="32" t="s">
+      <c r="AA18" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="125"/>
-      <c r="AD18" s="126"/>
-      <c r="AE18" s="124" t="s">
+      <c r="AB18" s="21"/>
+      <c r="AC18" s="93"/>
+      <c r="AD18" s="94"/>
+      <c r="AE18" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="AF18" s="125"/>
-      <c r="AG18" s="125"/>
-      <c r="AH18" s="125"/>
-      <c r="AI18" s="125"/>
-      <c r="AJ18" s="125"/>
-      <c r="AK18" s="126"/>
-      <c r="AL18" s="21"/>
-      <c r="AM18" s="22"/>
+      <c r="AF18" s="93"/>
+      <c r="AG18" s="93"/>
+      <c r="AH18" s="93"/>
+      <c r="AI18" s="93"/>
+      <c r="AJ18" s="93"/>
+      <c r="AK18" s="94"/>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="20"/>
       <c r="AN18" s="5"/>
       <c r="BK18" s="2"/>
     </row>
     <row r="19" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="45"/>
-      <c r="Z19" s="46"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="47"/>
-      <c r="AC19" s="64"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="127"/>
-      <c r="AF19" s="64"/>
-      <c r="AG19" s="64"/>
-      <c r="AH19" s="64"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="64"/>
-      <c r="AK19" s="65"/>
-      <c r="AL19" s="21"/>
-      <c r="AM19" s="22"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="110"/>
+      <c r="Y19" s="111"/>
+      <c r="Z19" s="112"/>
+      <c r="AA19" s="36"/>
+      <c r="AB19" s="113"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="95"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="96"/>
+      <c r="AH19" s="96"/>
+      <c r="AI19" s="96"/>
+      <c r="AJ19" s="96"/>
+      <c r="AK19" s="97"/>
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="20"/>
       <c r="AN19" s="5"/>
       <c r="BK19" s="2"/>
     </row>
     <row r="20" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="51"/>
-      <c r="Y20" s="45"/>
-      <c r="Z20" s="46"/>
-      <c r="AA20" s="42"/>
-      <c r="AB20" s="47"/>
-      <c r="AC20" s="64"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="127"/>
-      <c r="AF20" s="64"/>
-      <c r="AG20" s="64"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="64"/>
-      <c r="AJ20" s="64"/>
-      <c r="AK20" s="65"/>
-      <c r="AL20" s="21"/>
-      <c r="AM20" s="22"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="115"/>
+      <c r="X20" s="116"/>
+      <c r="Y20" s="111"/>
+      <c r="Z20" s="112"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="113"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="39"/>
+      <c r="AE20" s="95"/>
+      <c r="AF20" s="96"/>
+      <c r="AG20" s="96"/>
+      <c r="AH20" s="96"/>
+      <c r="AI20" s="96"/>
+      <c r="AJ20" s="96"/>
+      <c r="AK20" s="97"/>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="20"/>
       <c r="AN20" s="5"/>
       <c r="BK20" s="2"/>
     </row>
     <row r="21" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="55"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="45"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="42"/>
-      <c r="AB21" s="47"/>
-      <c r="AC21" s="64"/>
-      <c r="AD21" s="65"/>
-      <c r="AE21" s="127"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="65"/>
-      <c r="AL21" s="21"/>
-      <c r="AM21" s="22"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="112"/>
+      <c r="X21" s="116"/>
+      <c r="Y21" s="111"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="36"/>
+      <c r="AB21" s="113"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="39"/>
+      <c r="AE21" s="95"/>
+      <c r="AF21" s="96"/>
+      <c r="AG21" s="96"/>
+      <c r="AH21" s="96"/>
+      <c r="AI21" s="96"/>
+      <c r="AJ21" s="96"/>
+      <c r="AK21" s="97"/>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="20"/>
       <c r="AN21" s="5"/>
       <c r="BK21" s="2"/>
     </row>
     <row r="22" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="42"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="50"/>
-      <c r="X22" s="51"/>
-      <c r="Y22" s="45"/>
-      <c r="Z22" s="46"/>
-      <c r="AA22" s="42"/>
-      <c r="AB22" s="47"/>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="127"/>
-      <c r="AF22" s="64"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="21"/>
-      <c r="AM22" s="22"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="115"/>
+      <c r="X22" s="116"/>
+      <c r="Y22" s="111"/>
+      <c r="Z22" s="112"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="113"/>
+      <c r="AC22" s="38"/>
+      <c r="AD22" s="39"/>
+      <c r="AE22" s="95"/>
+      <c r="AF22" s="96"/>
+      <c r="AG22" s="96"/>
+      <c r="AH22" s="96"/>
+      <c r="AI22" s="96"/>
+      <c r="AJ22" s="96"/>
+      <c r="AK22" s="97"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="20"/>
       <c r="AN22" s="5"/>
       <c r="BK22" s="2"/>
     </row>
     <row r="23" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="42"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="51"/>
-      <c r="Y23" s="45"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="42"/>
-      <c r="AB23" s="47"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="127"/>
-      <c r="AF23" s="64"/>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="65"/>
-      <c r="AL23" s="21"/>
-      <c r="AM23" s="22"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="115"/>
+      <c r="X23" s="116"/>
+      <c r="Y23" s="111"/>
+      <c r="Z23" s="112"/>
+      <c r="AA23" s="36"/>
+      <c r="AB23" s="113"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="95"/>
+      <c r="AF23" s="96"/>
+      <c r="AG23" s="96"/>
+      <c r="AH23" s="96"/>
+      <c r="AI23" s="96"/>
+      <c r="AJ23" s="96"/>
+      <c r="AK23" s="97"/>
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="20"/>
       <c r="AN23" s="5"/>
       <c r="BK23" s="2"/>
     </row>
     <row r="24" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="51"/>
-      <c r="Y24" s="45"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="42"/>
-      <c r="AB24" s="47"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="127"/>
-      <c r="AF24" s="64"/>
-      <c r="AG24" s="64"/>
-      <c r="AH24" s="64"/>
-      <c r="AI24" s="64"/>
-      <c r="AJ24" s="64"/>
-      <c r="AK24" s="65"/>
-      <c r="AL24" s="21"/>
-      <c r="AM24" s="22"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="115"/>
+      <c r="X24" s="116"/>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="112"/>
+      <c r="AA24" s="36"/>
+      <c r="AB24" s="113"/>
+      <c r="AC24" s="38"/>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="95"/>
+      <c r="AF24" s="96"/>
+      <c r="AG24" s="96"/>
+      <c r="AH24" s="96"/>
+      <c r="AI24" s="96"/>
+      <c r="AJ24" s="96"/>
+      <c r="AK24" s="97"/>
+      <c r="AL24" s="19"/>
+      <c r="AM24" s="20"/>
       <c r="AN24" s="5"/>
       <c r="BK24" s="2"/>
     </row>
     <row r="25" spans="1:63" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="51"/>
-      <c r="Y25" s="45"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="42"/>
-      <c r="AB25" s="47"/>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="65"/>
-      <c r="AE25" s="127"/>
-      <c r="AF25" s="64"/>
-      <c r="AG25" s="64"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="64"/>
-      <c r="AJ25" s="64"/>
-      <c r="AK25" s="65"/>
-      <c r="AL25" s="21"/>
-      <c r="AM25" s="22"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="115"/>
+      <c r="X25" s="116"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="112"/>
+      <c r="AA25" s="36"/>
+      <c r="AB25" s="113"/>
+      <c r="AC25" s="38"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="95"/>
+      <c r="AF25" s="96"/>
+      <c r="AG25" s="96"/>
+      <c r="AH25" s="96"/>
+      <c r="AI25" s="96"/>
+      <c r="AJ25" s="96"/>
+      <c r="AK25" s="97"/>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="20"/>
       <c r="AN25" s="5"/>
       <c r="BK25" s="2"/>
     </row>
     <row r="26" spans="1:63" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="57"/>
-      <c r="U26" s="57"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="59"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="61"/>
-      <c r="AA26" s="62"/>
-      <c r="AB26" s="63"/>
-      <c r="AC26" s="64"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="127"/>
-      <c r="AF26" s="64"/>
-      <c r="AG26" s="64"/>
-      <c r="AH26" s="64"/>
-      <c r="AI26" s="64"/>
-      <c r="AJ26" s="64"/>
-      <c r="AK26" s="65"/>
-      <c r="AL26" s="21"/>
-      <c r="AM26" s="22"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="120"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="120"/>
+      <c r="S26" s="120"/>
+      <c r="T26" s="120"/>
+      <c r="U26" s="120"/>
+      <c r="V26" s="120"/>
+      <c r="W26" s="121"/>
+      <c r="X26" s="122"/>
+      <c r="Y26" s="123"/>
+      <c r="Z26" s="124"/>
+      <c r="AA26" s="120"/>
+      <c r="AB26" s="125"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="95"/>
+      <c r="AF26" s="96"/>
+      <c r="AG26" s="96"/>
+      <c r="AH26" s="96"/>
+      <c r="AI26" s="96"/>
+      <c r="AJ26" s="96"/>
+      <c r="AK26" s="97"/>
+      <c r="AL26" s="19"/>
+      <c r="AM26" s="20"/>
       <c r="AN26" s="5"/>
       <c r="BK26" s="2"/>
     </row>
